--- a/02_Flow_Cytometry/Figure_2_ROS_Source_Data.xlsx
+++ b/02_Flow_Cytometry/Figure_2_ROS_Source_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2237098_ed_ac_uk/Documents/PhD/Thesis/RSC EnvSciNano paper/Github data/02_Flow_Cytometry/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yazhini\OneDrive - University of Edinburgh\PhD\Thesis\RSC EnvSciNano paper\Github data\02_Flow_Cytometry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CFA2CEF5-1188-4D35-88A4-59842B4576E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C40AEBC5-DA46-48B9-83A6-A37395659C31}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA85090-7A7E-446E-82F5-00782A8EAFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3F22A25E-F1CF-4283-882C-B83C52BD1DF8}"/>
   </bookViews>
@@ -89,7 +89,236 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Positive control 50 </t>
+      <t>5 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2.5 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>20 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>40 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>80 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>160 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>320 mg L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PS NP</t>
+    </r>
+  </si>
+  <si>
+    <t>Figure 2</t>
+  </si>
+  <si>
+    <t>Assay: Intracellular ROS using H2DCFDA</t>
+  </si>
+  <si>
+    <t>Instrument: BD LSR Fortessa</t>
+  </si>
+  <si>
+    <t>Replicates: duplicate experiments</t>
+  </si>
+  <si>
+    <t>Exposure times: 3 h and 24 h</t>
+  </si>
+  <si>
+    <t>Error bars: SD</t>
+  </si>
+  <si>
+    <t>Reported metric: Mean Fluoresence Intensity</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Positve Control with 50 </t>
     </r>
     <r>
       <rPr>
@@ -129,235 +358,6 @@
       </rPr>
       <t>2</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>5 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2.5 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>20 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>10 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>40 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>80 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>160 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>320 mg L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PS NP</t>
-    </r>
-  </si>
-  <si>
-    <t>Figure 2</t>
-  </si>
-  <si>
-    <t>Assay: Intracellular ROS using H2DCFDA</t>
-  </si>
-  <si>
-    <t>Instrument: BD LSR Fortessa</t>
-  </si>
-  <si>
-    <t>Replicates: duplicate experiments</t>
-  </si>
-  <si>
-    <t>Exposure times: 3 h and 24 h</t>
-  </si>
-  <si>
-    <t>Error bars: SD</t>
-  </si>
-  <si>
-    <t>Reported metric: Mean Fluoresence Intensity</t>
   </si>
 </sst>
 </file>
@@ -389,6 +389,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -400,12 +406,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -545,15 +545,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -571,6 +569,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,10 +597,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -909,389 +916,390 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161FD036-407B-4DB1-8002-6F9CF9770B46}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.7265625" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="10" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="9"/>
-      <c r="C9" s="5" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="7"/>
+      <c r="C10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H10" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I10" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J10" s="15" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1.56</v>
-      </c>
-      <c r="D10">
-        <v>1.57</v>
-      </c>
-      <c r="E10">
-        <v>1.5649999999999999</v>
-      </c>
-      <c r="F10" s="4">
-        <v>7.0699999999999999E-3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3.58</v>
-      </c>
-      <c r="H10">
-        <v>3.49</v>
-      </c>
-      <c r="I10">
-        <v>3.5350000000000001</v>
-      </c>
-      <c r="J10" s="4">
-        <v>6.3640000000000002E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1.74</v>
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.56</v>
       </c>
       <c r="D11">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="E11">
-        <v>1.75</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1.414E-2</v>
-      </c>
-      <c r="G11" s="3">
-        <v>7.04</v>
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.0699999999999999E-3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3.58</v>
       </c>
       <c r="H11">
-        <v>6.45</v>
+        <v>3.49</v>
       </c>
       <c r="I11">
-        <v>6.7450000000000001</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0.41719000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>3.5350000000000001</v>
+      </c>
+      <c r="J11" s="3">
+        <v>6.3640000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
+        <v>1.74</v>
+      </c>
+      <c r="D12">
+        <v>1.76</v>
+      </c>
+      <c r="E12">
+        <v>1.75</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.414E-2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7.04</v>
+      </c>
+      <c r="H12">
+        <v>6.45</v>
+      </c>
+      <c r="I12">
+        <v>6.7450000000000001</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.41719000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
         <v>1.94</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2.0099999999999998</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>1.9750000000000001</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F13" s="3">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G13" s="2">
         <v>7.35</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>6.81</v>
       </c>
-      <c r="I12">
+      <c r="I13">
         <v>7.08</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J13" s="3">
         <v>0.38184000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3.57</v>
-      </c>
-      <c r="D13">
-        <v>3.65</v>
-      </c>
-      <c r="E13">
-        <v>3.61</v>
-      </c>
-      <c r="F13" s="4">
-        <v>5.6570000000000002E-2</v>
-      </c>
-      <c r="G13" s="3">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="H13">
-        <v>8.4700000000000006</v>
-      </c>
-      <c r="I13">
-        <v>8.8849999999999998</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0.58689999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
+        <v>3.57</v>
+      </c>
+      <c r="D14">
+        <v>3.65</v>
+      </c>
+      <c r="E14">
+        <v>3.61</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.6570000000000002E-2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H14">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="I14">
+        <v>8.8849999999999998</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.58689999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2">
         <v>3.1</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>3.2</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>3.15</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="3">
         <v>7.0709999999999995E-2</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G15" s="2">
         <v>8.17</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>7.78</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>7.9749999999999996</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J15" s="3">
         <v>0.27577000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.08</v>
+      </c>
+      <c r="D16">
+        <v>3.18</v>
+      </c>
+      <c r="E16">
+        <v>3.13</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7.0709999999999995E-2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="H16">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="I16">
+        <v>8.4149999999999991</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.28991</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3">
-        <v>3.08</v>
-      </c>
-      <c r="D15">
-        <v>3.18</v>
-      </c>
-      <c r="E15">
-        <v>3.13</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="C17" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="D17">
+        <v>3.44</v>
+      </c>
+      <c r="E17">
+        <v>3.37</v>
+      </c>
+      <c r="F17" s="3">
+        <v>9.8989999999999995E-2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7.55</v>
+      </c>
+      <c r="H17">
+        <v>7.14</v>
+      </c>
+      <c r="I17">
+        <v>7.3449999999999998</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.28991</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3.41</v>
+      </c>
+      <c r="D18">
+        <v>3.51</v>
+      </c>
+      <c r="E18">
+        <v>3.46</v>
+      </c>
+      <c r="F18" s="3">
         <v>7.0709999999999995E-2</v>
       </c>
-      <c r="G15" s="3">
-        <v>8.6199999999999992</v>
-      </c>
-      <c r="H15">
-        <v>8.2100000000000009</v>
-      </c>
-      <c r="I15">
-        <v>8.4149999999999991</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.28991</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="D16">
-        <v>3.44</v>
-      </c>
-      <c r="E16">
-        <v>3.37</v>
-      </c>
-      <c r="F16" s="4">
-        <v>9.8989999999999995E-2</v>
-      </c>
-      <c r="G16" s="3">
-        <v>7.55</v>
-      </c>
-      <c r="H16">
-        <v>7.14</v>
-      </c>
-      <c r="I16">
-        <v>7.3449999999999998</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0.28991</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="1" t="s">
+      <c r="G18" s="2">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>7.93</v>
+      </c>
+      <c r="I18">
+        <v>8.4649999999999999</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.75660000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="3">
-        <v>3.41</v>
-      </c>
-      <c r="D17">
-        <v>3.51</v>
-      </c>
-      <c r="E17">
-        <v>3.46</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="C19" s="2">
+        <v>2.86</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3.04</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2.95</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.12728</v>
+      </c>
+      <c r="G19" s="2">
+        <v>5.31</v>
+      </c>
+      <c r="H19" s="11">
+        <v>5.08</v>
+      </c>
+      <c r="I19" s="11">
+        <v>5.1950000000000003</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.16263</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4">
+        <v>67.7</v>
+      </c>
+      <c r="D20" s="4">
+        <v>67.8</v>
+      </c>
+      <c r="E20" s="4">
+        <v>67.75</v>
+      </c>
+      <c r="F20" s="4">
         <v>7.0709999999999995E-2</v>
       </c>
-      <c r="G17" s="3">
-        <v>9</v>
-      </c>
-      <c r="H17">
-        <v>7.93</v>
-      </c>
-      <c r="I17">
-        <v>8.4649999999999999</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0.75660000000000005</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2.86</v>
-      </c>
-      <c r="D18">
-        <v>3.04</v>
-      </c>
-      <c r="E18">
-        <v>2.95</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0.12728</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5.31</v>
-      </c>
-      <c r="H18">
-        <v>5.08</v>
-      </c>
-      <c r="I18">
-        <v>5.1950000000000003</v>
-      </c>
-      <c r="J18" s="4">
-        <v>0.16263</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="16.5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
+      <c r="G20" s="4">
         <v>91.2</v>
       </c>
-      <c r="D19" s="6">
+      <c r="H20" s="4">
         <v>91.5</v>
       </c>
-      <c r="E19" s="6">
+      <c r="I20" s="4">
         <v>91.35</v>
       </c>
-      <c r="F19" s="7">
+      <c r="J20" s="5">
         <v>0.21213000000000001</v>
-      </c>
-      <c r="G19" s="5">
-        <v>67.7</v>
-      </c>
-      <c r="H19" s="6">
-        <v>67.8</v>
-      </c>
-      <c r="I19" s="6">
-        <v>67.75</v>
-      </c>
-      <c r="J19" s="7">
-        <v>7.0709999999999995E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:J9"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>